--- a/examples/military_units.xlsx
+++ b/examples/military_units.xlsx
@@ -444,7 +444,7 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Личный номер</t>
+          <t>л/н</t>
         </is>
       </c>
     </row>
